--- a/artfynd/A 31182-2025 artfynd.xlsx
+++ b/artfynd/A 31182-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89119744</v>
+        <v>93542711</v>
       </c>
       <c r="B2" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sjudartjärnen med omgivningar, Hls</t>
+          <t>Sjudarberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533589.9922481314</v>
+        <v>533491</v>
       </c>
       <c r="R2" t="n">
-        <v>6908871.854692549</v>
+        <v>6908717</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,35 +760,30 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
+          <t>Ecogain</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89119745</v>
+        <v>89119715</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533618.8056915735</v>
+        <v>533409</v>
       </c>
       <c r="R3" t="n">
-        <v>6908878.189374534</v>
+        <v>6908601</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,19 +844,9 @@
           <t>2020-07-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89119743</v>
+        <v>89119745</v>
       </c>
       <c r="B4" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533565.099818512</v>
+        <v>533619</v>
       </c>
       <c r="R4" t="n">
-        <v>6908846.026027545</v>
+        <v>6908878</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,19 +945,9 @@
           <t>2020-07-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-07-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,53 +978,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>93542709</v>
+        <v>89119744</v>
       </c>
       <c r="B5" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjudarberget, Hls</t>
+          <t>Sjudartjärnen med omgivningar, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533600.0701841166</v>
+        <v>533590</v>
       </c>
       <c r="R5" t="n">
-        <v>6908888.698463818</v>
+        <v>6908872</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,22 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,53 +1063,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Ecogain</t>
+          <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>93542711</v>
+        <v>93542709</v>
       </c>
       <c r="B6" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533490.930934045</v>
+        <v>533600</v>
       </c>
       <c r="R6" t="n">
-        <v>6908717.384347304</v>
+        <v>6908889</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2021-04-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-04-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,64 +1180,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94778687</v>
+        <v>93542708</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sjudarberget, V branten, Hls</t>
+          <t>Sjudarberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533481.582226639</v>
+        <v>533656</v>
       </c>
       <c r="R7" t="n">
-        <v>6908674.036350615</v>
+        <v>6908869</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,27 +1254,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Min antal</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1284,233 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>94778687</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sjudarberget, V branten, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>533481</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6908674</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-07-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-07-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Min antal</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Johan Råghall</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Johan Råghall</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>89119743</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sjudartjärnen med omgivningar, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>533565</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6908846</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-07-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-07-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
